--- a/Mass_update_KAIKU/mass_update_kaiku_hierarchy_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_hierarchy_fix.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0RQQ00000KlaVx</t>
+          <t>a0RQQ00000KlZWi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KAIKU SOFTWARE</t>
+          <t>Kaiku</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>1570000020S</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0RQQ00000KlZWj</t>
+          <t>a0RQQ00000KlaVx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PATIENT COMPANION MO SUBS</t>
+          <t>KAIKU SOFTWARE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15700000026</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000KlZWi</t>
+          <t>a0RQQ00000KlZWj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kaiku</t>
+          <t>PATIENT COMPANION MO SUBS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1570000020S</t>
+          <t>15700000026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPj</t>
+          <t>a0RQQ00000HMjPq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
+          <t>ESI CCDA EXPORT SW: MSQ-KAIKU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPh</t>
+          <t>a0RQQ00000HMjPp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MODULE FOR SURVIVORSHIP PATIEN</t>
+          <t>ESI PRO IMP SW: MSQ-KAIKU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPp</t>
+          <t>a0RQQ00000HMjPo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESI PRO IMP SW: MSQ-KAIKU</t>
+          <t>ESI SCHEDULE EXPORT: MSQ-Kaiku</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPq</t>
+          <t>a0RQQ00000HMjPj</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESI CCDA EXPORT SW: MSQ-KAIKU</t>
+          <t>MODULE FOR RADIOTHERAPY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPo</t>
+          <t>a0RQQ00000HMjPh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESI SCHEDULE EXPORT: MSQ-Kaiku</t>
+          <t>MODULE FOR SURVIVORSHIP PATIEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMFpq</t>
+          <t>a0RQQ00000HMFpr</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESI PRO IMP SW: MSQ-KAIKU</t>
+          <t>ESI CCDA EXPORT SW: MSQ-KAIKU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMFpr</t>
+          <t>a0RQQ00000HMFpq</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESI CCDA EXPORT SW: MSQ-KAIKU</t>
+          <t>ESI PRO IMP SW: MSQ-KAIKU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
